--- a/artfynd/A 57380-2020 artfynd.xlsx
+++ b/artfynd/A 57380-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121756555</v>
+        <v>121756513</v>
       </c>
       <c r="B2" t="n">
-        <v>78616</v>
+        <v>74714</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477398</v>
+        <v>477390</v>
       </c>
       <c r="R2" t="n">
-        <v>6593192</v>
+        <v>6593251</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121756601</v>
+        <v>121756651</v>
       </c>
       <c r="B3" t="n">
-        <v>95651</v>
+        <v>56569</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,31 +793,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>54</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogstrappmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Anastrophyllum michauxii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(F.Weber.) H.Buch</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -825,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477377</v>
+        <v>477348</v>
       </c>
       <c r="R3" t="n">
-        <v>6593144</v>
+        <v>6592989</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -869,7 +881,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -994,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121756513</v>
+        <v>121756609</v>
       </c>
       <c r="B5" t="n">
-        <v>74714</v>
+        <v>57357</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1010,26 +1021,35 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1037,10 +1057,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477390</v>
+        <v>477337</v>
       </c>
       <c r="R5" t="n">
-        <v>6593251</v>
+        <v>6593139</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1081,7 +1101,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1100,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121756651</v>
+        <v>121756618</v>
       </c>
       <c r="B6" t="n">
-        <v>56569</v>
+        <v>79205</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1112,43 +1131,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1156,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477348</v>
+        <v>477372</v>
       </c>
       <c r="R6" t="n">
-        <v>6592989</v>
+        <v>6593018</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1200,6 +1206,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1218,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121756609</v>
+        <v>121756601</v>
       </c>
       <c r="B7" t="n">
-        <v>57357</v>
+        <v>95651</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1234,35 +1241,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>54</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogstrappmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Anastrophyllum michauxii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(F.Weber.) H.Buch</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1270,10 +1269,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477337</v>
+        <v>477377</v>
       </c>
       <c r="R7" t="n">
-        <v>6593139</v>
+        <v>6593144</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1314,6 +1313,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1332,10 +1332,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121756618</v>
+        <v>121756555</v>
       </c>
       <c r="B8" t="n">
-        <v>79205</v>
+        <v>78616</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1348,21 +1348,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477372</v>
+        <v>477398</v>
       </c>
       <c r="R8" t="n">
-        <v>6593018</v>
+        <v>6593192</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>

--- a/artfynd/A 57380-2020 artfynd.xlsx
+++ b/artfynd/A 57380-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121756513</v>
+        <v>121756519</v>
       </c>
       <c r="B2" t="n">
-        <v>74714</v>
+        <v>90693</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>308</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477390</v>
+        <v>477326</v>
       </c>
       <c r="R2" t="n">
-        <v>6593251</v>
+        <v>6593253</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121756651</v>
+        <v>121756513</v>
       </c>
       <c r="B3" t="n">
-        <v>56569</v>
+        <v>74714</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,43 +793,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -837,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477348</v>
+        <v>477390</v>
       </c>
       <c r="R3" t="n">
-        <v>6592989</v>
+        <v>6593251</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -881,6 +868,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -899,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121756519</v>
+        <v>121756609</v>
       </c>
       <c r="B4" t="n">
-        <v>90693</v>
+        <v>57357</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,30 +899,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -942,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477326</v>
+        <v>477337</v>
       </c>
       <c r="R4" t="n">
-        <v>6593253</v>
+        <v>6593139</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -986,7 +983,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1005,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121756609</v>
+        <v>121756651</v>
       </c>
       <c r="B5" t="n">
-        <v>57357</v>
+        <v>56569</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,25 +1013,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1044,10 +1040,14 @@
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477337</v>
+        <v>477348</v>
       </c>
       <c r="R5" t="n">
-        <v>6593139</v>
+        <v>6592989</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121756618</v>
+        <v>121756601</v>
       </c>
       <c r="B6" t="n">
-        <v>79205</v>
+        <v>95651</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,26 +1135,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229821</v>
+        <v>54</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Skogstrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Anastrophyllum michauxii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(F.Weber.) H.Buch</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1162,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477372</v>
+        <v>477377</v>
       </c>
       <c r="R6" t="n">
-        <v>6593018</v>
+        <v>6593144</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1225,10 +1226,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121756601</v>
+        <v>121756618</v>
       </c>
       <c r="B7" t="n">
-        <v>95651</v>
+        <v>79205</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1241,27 +1242,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>54</v>
+        <v>229821</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogstrappmossa</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Anastrophyllum michauxii</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(F.Weber.) H.Buch</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1269,10 +1269,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477377</v>
+        <v>477372</v>
       </c>
       <c r="R7" t="n">
-        <v>6593144</v>
+        <v>6593018</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>

--- a/artfynd/A 57380-2020 artfynd.xlsx
+++ b/artfynd/A 57380-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121756519</v>
+        <v>121756601</v>
       </c>
       <c r="B2" t="n">
-        <v>90693</v>
+        <v>95651</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>54</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skogstrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Anastrophyllum michauxii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(F.Weber.) H.Buch</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477326</v>
+        <v>477377</v>
       </c>
       <c r="R2" t="n">
-        <v>6593253</v>
+        <v>6593144</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121756513</v>
+        <v>121756618</v>
       </c>
       <c r="B3" t="n">
-        <v>74714</v>
+        <v>79205</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>308</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477390</v>
+        <v>477372</v>
       </c>
       <c r="R3" t="n">
-        <v>6593251</v>
+        <v>6593018</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -887,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121756609</v>
+        <v>121756519</v>
       </c>
       <c r="B4" t="n">
-        <v>57357</v>
+        <v>90693</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,39 +900,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -939,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477337</v>
+        <v>477326</v>
       </c>
       <c r="R4" t="n">
-        <v>6593139</v>
+        <v>6593253</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -983,6 +975,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1119,10 +1112,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121756601</v>
+        <v>121756609</v>
       </c>
       <c r="B6" t="n">
-        <v>95651</v>
+        <v>57357</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,27 +1128,35 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>54</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogstrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Anastrophyllum michauxii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(F.Weber.) H.Buch</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1163,10 +1164,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477377</v>
+        <v>477337</v>
       </c>
       <c r="R6" t="n">
-        <v>6593144</v>
+        <v>6593139</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1207,7 +1208,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1226,10 +1226,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121756618</v>
+        <v>121756513</v>
       </c>
       <c r="B7" t="n">
-        <v>79205</v>
+        <v>74714</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1242,21 +1242,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>308</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1269,10 +1269,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477372</v>
+        <v>477390</v>
       </c>
       <c r="R7" t="n">
-        <v>6593018</v>
+        <v>6593251</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>

--- a/artfynd/A 57380-2020 artfynd.xlsx
+++ b/artfynd/A 57380-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121756601</v>
+        <v>121756651</v>
       </c>
       <c r="B2" t="n">
-        <v>95651</v>
+        <v>56569</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>54</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogstrappmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Anastrophyllum michauxii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(F.Weber.) H.Buch</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +731,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477377</v>
+        <v>477348</v>
       </c>
       <c r="R2" t="n">
-        <v>6593144</v>
+        <v>6592989</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -763,7 +775,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -888,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121756519</v>
+        <v>121756601</v>
       </c>
       <c r="B4" t="n">
-        <v>90693</v>
+        <v>95651</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,30 +911,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>54</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skogstrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Anastrophyllum michauxii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(F.Weber.) H.Buch</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -931,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477326</v>
+        <v>477377</v>
       </c>
       <c r="R4" t="n">
-        <v>6593253</v>
+        <v>6593144</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -994,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121756651</v>
+        <v>121756609</v>
       </c>
       <c r="B5" t="n">
-        <v>56569</v>
+        <v>57357</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1006,25 +1018,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1033,14 +1045,10 @@
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1050,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477348</v>
+        <v>477337</v>
       </c>
       <c r="R5" t="n">
-        <v>6592989</v>
+        <v>6593139</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1112,10 +1120,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121756609</v>
+        <v>121756555</v>
       </c>
       <c r="B6" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1128,35 +1136,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1164,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477337</v>
+        <v>477398</v>
       </c>
       <c r="R6" t="n">
-        <v>6593139</v>
+        <v>6593192</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1208,6 +1207,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1332,10 +1332,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121756555</v>
+        <v>121756519</v>
       </c>
       <c r="B8" t="n">
-        <v>78616</v>
+        <v>90693</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1344,25 +1344,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477398</v>
+        <v>477326</v>
       </c>
       <c r="R8" t="n">
-        <v>6593192</v>
+        <v>6593253</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>

--- a/artfynd/A 57380-2020 artfynd.xlsx
+++ b/artfynd/A 57380-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121756651</v>
+        <v>121756601</v>
       </c>
       <c r="B2" t="n">
-        <v>56569</v>
+        <v>95651</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>54</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skogstrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Anastrophyllum michauxii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(F.Weber.) H.Buch</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -731,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477348</v>
+        <v>477377</v>
       </c>
       <c r="R2" t="n">
-        <v>6592989</v>
+        <v>6593144</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -775,6 +763,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -793,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121756618</v>
+        <v>121756555</v>
       </c>
       <c r="B3" t="n">
-        <v>79205</v>
+        <v>78616</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -836,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477372</v>
+        <v>477398</v>
       </c>
       <c r="R3" t="n">
-        <v>6593018</v>
+        <v>6593192</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -899,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121756601</v>
+        <v>121756618</v>
       </c>
       <c r="B4" t="n">
-        <v>95651</v>
+        <v>79205</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,27 +904,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>54</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogstrappmossa</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Anastrophyllum michauxii</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(F.Weber.) H.Buch</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -943,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477377</v>
+        <v>477372</v>
       </c>
       <c r="R4" t="n">
-        <v>6593144</v>
+        <v>6593018</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1006,10 +994,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121756609</v>
+        <v>121756513</v>
       </c>
       <c r="B5" t="n">
-        <v>57357</v>
+        <v>74714</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,35 +1010,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1058,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477337</v>
+        <v>477390</v>
       </c>
       <c r="R5" t="n">
-        <v>6593139</v>
+        <v>6593251</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1102,6 +1081,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1120,10 +1100,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121756555</v>
+        <v>121756609</v>
       </c>
       <c r="B6" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1136,26 +1116,35 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1163,10 +1152,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477398</v>
+        <v>477337</v>
       </c>
       <c r="R6" t="n">
-        <v>6593192</v>
+        <v>6593139</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1207,7 +1196,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1226,10 +1214,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121756513</v>
+        <v>121756519</v>
       </c>
       <c r="B7" t="n">
-        <v>74714</v>
+        <v>90693</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1238,25 +1226,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>308</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1269,10 +1257,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477390</v>
+        <v>477326</v>
       </c>
       <c r="R7" t="n">
-        <v>6593251</v>
+        <v>6593253</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1332,10 +1320,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121756519</v>
+        <v>121756651</v>
       </c>
       <c r="B8" t="n">
-        <v>90693</v>
+        <v>56569</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1348,26 +1336,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1375,10 +1376,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477326</v>
+        <v>477348</v>
       </c>
       <c r="R8" t="n">
-        <v>6593253</v>
+        <v>6592989</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1419,7 +1420,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 57380-2020 artfynd.xlsx
+++ b/artfynd/A 57380-2020 artfynd.xlsx
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121756618</v>
+        <v>121756519</v>
       </c>
       <c r="B4" t="n">
-        <v>79205</v>
+        <v>90693</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,25 +900,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477372</v>
+        <v>477326</v>
       </c>
       <c r="R4" t="n">
-        <v>6593018</v>
+        <v>6593253</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1100,10 +1100,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121756609</v>
+        <v>121756618</v>
       </c>
       <c r="B6" t="n">
-        <v>57357</v>
+        <v>79205</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1116,35 +1116,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1152,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477337</v>
+        <v>477372</v>
       </c>
       <c r="R6" t="n">
-        <v>6593139</v>
+        <v>6593018</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1196,6 +1187,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1214,10 +1206,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121756519</v>
+        <v>121756609</v>
       </c>
       <c r="B7" t="n">
-        <v>90693</v>
+        <v>57357</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,30 +1218,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1257,10 +1258,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477326</v>
+        <v>477337</v>
       </c>
       <c r="R7" t="n">
-        <v>6593253</v>
+        <v>6593139</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1301,7 +1302,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 57380-2020 artfynd.xlsx
+++ b/artfynd/A 57380-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121756601</v>
+        <v>121756555</v>
       </c>
       <c r="B2" t="n">
-        <v>95651</v>
+        <v>78629</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,27 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>54</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogstrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Anastrophyllum michauxii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(F.Weber.) H.Buch</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477377</v>
+        <v>477398</v>
       </c>
       <c r="R2" t="n">
-        <v>6593144</v>
+        <v>6593192</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -782,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121756555</v>
+        <v>121756519</v>
       </c>
       <c r="B3" t="n">
-        <v>78616</v>
+        <v>90707</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -825,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477398</v>
+        <v>477326</v>
       </c>
       <c r="R3" t="n">
-        <v>6593192</v>
+        <v>6593253</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -888,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121756519</v>
+        <v>121756601</v>
       </c>
       <c r="B4" t="n">
-        <v>90693</v>
+        <v>95669</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,30 +899,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>54</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skogstrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Anastrophyllum michauxii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(F.Weber.) H.Buch</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477326</v>
+        <v>477377</v>
       </c>
       <c r="R4" t="n">
-        <v>6593253</v>
+        <v>6593144</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -994,10 +994,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121756513</v>
+        <v>121756609</v>
       </c>
       <c r="B5" t="n">
-        <v>74714</v>
+        <v>57365</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1010,26 +1010,35 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1037,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477390</v>
+        <v>477337</v>
       </c>
       <c r="R5" t="n">
-        <v>6593251</v>
+        <v>6593139</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1081,7 +1090,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1100,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121756618</v>
+        <v>121756651</v>
       </c>
       <c r="B6" t="n">
-        <v>79205</v>
+        <v>56577</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1112,30 +1120,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1143,10 +1164,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477372</v>
+        <v>477348</v>
       </c>
       <c r="R6" t="n">
-        <v>6593018</v>
+        <v>6592989</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1187,7 +1208,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1206,10 +1226,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121756609</v>
+        <v>121756513</v>
       </c>
       <c r="B7" t="n">
-        <v>57357</v>
+        <v>74727</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,35 +1242,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1258,10 +1269,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477337</v>
+        <v>477390</v>
       </c>
       <c r="R7" t="n">
-        <v>6593139</v>
+        <v>6593251</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1302,6 +1313,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1320,10 +1332,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121756651</v>
+        <v>121756618</v>
       </c>
       <c r="B8" t="n">
-        <v>56569</v>
+        <v>79218</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1332,43 +1344,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1376,10 +1375,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477348</v>
+        <v>477372</v>
       </c>
       <c r="R8" t="n">
-        <v>6592989</v>
+        <v>6593018</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1420,6 +1419,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 57380-2020 artfynd.xlsx
+++ b/artfynd/A 57380-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121756555</v>
+        <v>121756609</v>
       </c>
       <c r="B2" t="n">
-        <v>78629</v>
+        <v>57365</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,35 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477398</v>
+        <v>477337</v>
       </c>
       <c r="R2" t="n">
-        <v>6593192</v>
+        <v>6593139</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -762,7 +771,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -781,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121756519</v>
+        <v>121756513</v>
       </c>
       <c r="B3" t="n">
-        <v>90707</v>
+        <v>74729</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +801,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477326</v>
+        <v>477390</v>
       </c>
       <c r="R3" t="n">
-        <v>6593253</v>
+        <v>6593251</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -887,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121756601</v>
+        <v>121756519</v>
       </c>
       <c r="B4" t="n">
-        <v>95669</v>
+        <v>90709</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,31 +907,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>54</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogstrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Anastrophyllum michauxii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(F.Weber.) H.Buch</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -931,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477377</v>
+        <v>477326</v>
       </c>
       <c r="R4" t="n">
-        <v>6593144</v>
+        <v>6593253</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -994,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121756609</v>
+        <v>121756555</v>
       </c>
       <c r="B5" t="n">
-        <v>57365</v>
+        <v>78631</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1010,35 +1017,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1046,10 +1044,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477337</v>
+        <v>477398</v>
       </c>
       <c r="R5" t="n">
-        <v>6593139</v>
+        <v>6593192</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1090,6 +1088,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1108,10 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121756651</v>
+        <v>121756618</v>
       </c>
       <c r="B6" t="n">
-        <v>56577</v>
+        <v>79220</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1120,43 +1119,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1164,10 +1150,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477348</v>
+        <v>477372</v>
       </c>
       <c r="R6" t="n">
-        <v>6592989</v>
+        <v>6593018</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1208,6 +1194,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1226,10 +1213,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121756513</v>
+        <v>121756601</v>
       </c>
       <c r="B7" t="n">
-        <v>74727</v>
+        <v>95671</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1242,26 +1229,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>308</v>
+        <v>54</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Skogstrappmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Anastrophyllum michauxii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(F.Weber.) H.Buch</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1269,10 +1257,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477390</v>
+        <v>477377</v>
       </c>
       <c r="R7" t="n">
-        <v>6593251</v>
+        <v>6593144</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1332,10 +1320,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121756618</v>
+        <v>121756651</v>
       </c>
       <c r="B8" t="n">
-        <v>79218</v>
+        <v>56577</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1344,30 +1332,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1375,10 +1376,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477372</v>
+        <v>477348</v>
       </c>
       <c r="R8" t="n">
-        <v>6593018</v>
+        <v>6592989</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1419,7 +1420,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 57380-2020 artfynd.xlsx
+++ b/artfynd/A 57380-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121756609</v>
+        <v>121756555</v>
       </c>
       <c r="B2" t="n">
-        <v>57365</v>
+        <v>78632</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,35 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477337</v>
+        <v>477398</v>
       </c>
       <c r="R2" t="n">
-        <v>6593139</v>
+        <v>6593192</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -771,6 +762,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121756513</v>
+        <v>121756651</v>
       </c>
       <c r="B3" t="n">
-        <v>74729</v>
+        <v>56577</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,30 +793,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>308</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -832,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477390</v>
+        <v>477348</v>
       </c>
       <c r="R3" t="n">
-        <v>6593251</v>
+        <v>6592989</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -876,7 +881,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -895,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121756519</v>
+        <v>121756609</v>
       </c>
       <c r="B4" t="n">
-        <v>90709</v>
+        <v>57365</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -907,30 +911,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -938,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477326</v>
+        <v>477337</v>
       </c>
       <c r="R4" t="n">
-        <v>6593253</v>
+        <v>6593139</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -982,7 +995,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1001,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121756555</v>
+        <v>121756519</v>
       </c>
       <c r="B5" t="n">
-        <v>78631</v>
+        <v>90710</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1013,25 +1025,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1044,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477398</v>
+        <v>477326</v>
       </c>
       <c r="R5" t="n">
-        <v>6593192</v>
+        <v>6593253</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1110,7 +1122,7 @@
         <v>121756618</v>
       </c>
       <c r="B6" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1216,7 +1228,7 @@
         <v>121756601</v>
       </c>
       <c r="B7" t="n">
-        <v>95671</v>
+        <v>95678</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1320,10 +1332,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121756651</v>
+        <v>121756513</v>
       </c>
       <c r="B8" t="n">
-        <v>56577</v>
+        <v>74729</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1332,43 +1344,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>308</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1376,10 +1375,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477348</v>
+        <v>477390</v>
       </c>
       <c r="R8" t="n">
-        <v>6592989</v>
+        <v>6593251</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1420,6 +1419,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 57380-2020 artfynd.xlsx
+++ b/artfynd/A 57380-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121756555</v>
+        <v>121756651</v>
       </c>
       <c r="B2" t="n">
-        <v>78632</v>
+        <v>56581</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +731,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477398</v>
+        <v>477348</v>
       </c>
       <c r="R2" t="n">
-        <v>6593192</v>
+        <v>6592989</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -762,7 +775,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -781,10 +793,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121756651</v>
+        <v>121756519</v>
       </c>
       <c r="B3" t="n">
-        <v>56577</v>
+        <v>90719</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,39 +809,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -837,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477348</v>
+        <v>477326</v>
       </c>
       <c r="R3" t="n">
-        <v>6592989</v>
+        <v>6593253</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -881,6 +880,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -902,7 +902,7 @@
         <v>121756609</v>
       </c>
       <c r="B4" t="n">
-        <v>57365</v>
+        <v>57369</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1013,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121756519</v>
+        <v>121756513</v>
       </c>
       <c r="B5" t="n">
-        <v>90710</v>
+        <v>74733</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1025,25 +1025,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477326</v>
+        <v>477390</v>
       </c>
       <c r="R5" t="n">
-        <v>6593253</v>
+        <v>6593251</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121756618</v>
+        <v>121756601</v>
       </c>
       <c r="B6" t="n">
-        <v>79221</v>
+        <v>95687</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,26 +1135,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229821</v>
+        <v>54</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Skogstrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Anastrophyllum michauxii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(F.Weber.) H.Buch</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1162,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477372</v>
+        <v>477377</v>
       </c>
       <c r="R6" t="n">
-        <v>6593018</v>
+        <v>6593144</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1225,10 +1226,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121756601</v>
+        <v>121756618</v>
       </c>
       <c r="B7" t="n">
-        <v>95678</v>
+        <v>79228</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1241,27 +1242,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>54</v>
+        <v>229821</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogstrappmossa</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Anastrophyllum michauxii</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(F.Weber.) H.Buch</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1269,10 +1269,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477377</v>
+        <v>477372</v>
       </c>
       <c r="R7" t="n">
-        <v>6593144</v>
+        <v>6593018</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1332,10 +1332,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121756513</v>
+        <v>121756555</v>
       </c>
       <c r="B8" t="n">
-        <v>74729</v>
+        <v>78639</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1348,21 +1348,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477390</v>
+        <v>477398</v>
       </c>
       <c r="R8" t="n">
-        <v>6593251</v>
+        <v>6593192</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>

--- a/artfynd/A 57380-2020 artfynd.xlsx
+++ b/artfynd/A 57380-2020 artfynd.xlsx
@@ -793,10 +793,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121756519</v>
+        <v>121756609</v>
       </c>
       <c r="B3" t="n">
-        <v>90719</v>
+        <v>57369</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,30 +805,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -836,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477326</v>
+        <v>477337</v>
       </c>
       <c r="R3" t="n">
-        <v>6593253</v>
+        <v>6593139</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -880,7 +889,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -899,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121756609</v>
+        <v>121756519</v>
       </c>
       <c r="B4" t="n">
-        <v>57369</v>
+        <v>90719</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,39 +919,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -951,10 +950,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477337</v>
+        <v>477326</v>
       </c>
       <c r="R4" t="n">
-        <v>6593139</v>
+        <v>6593253</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -995,6 +994,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121756601</v>
+        <v>121756618</v>
       </c>
       <c r="B6" t="n">
-        <v>95687</v>
+        <v>79228</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,27 +1135,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>54</v>
+        <v>229821</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogstrappmossa</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Anastrophyllum michauxii</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(F.Weber.) H.Buch</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1163,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477377</v>
+        <v>477372</v>
       </c>
       <c r="R6" t="n">
-        <v>6593144</v>
+        <v>6593018</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1226,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121756618</v>
+        <v>121756601</v>
       </c>
       <c r="B7" t="n">
-        <v>79228</v>
+        <v>95687</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1242,26 +1241,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>54</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Skogstrappmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Anastrophyllum michauxii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(F.Weber.) H.Buch</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1269,10 +1269,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477372</v>
+        <v>477377</v>
       </c>
       <c r="R7" t="n">
-        <v>6593018</v>
+        <v>6593144</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>

--- a/artfynd/A 57380-2020 artfynd.xlsx
+++ b/artfynd/A 57380-2020 artfynd.xlsx
@@ -793,10 +793,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121756609</v>
+        <v>121756519</v>
       </c>
       <c r="B3" t="n">
-        <v>57369</v>
+        <v>90719</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,39 +805,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -845,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477337</v>
+        <v>477326</v>
       </c>
       <c r="R3" t="n">
-        <v>6593139</v>
+        <v>6593253</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -889,6 +880,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -907,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121756519</v>
+        <v>121756609</v>
       </c>
       <c r="B4" t="n">
-        <v>90719</v>
+        <v>57369</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,30 +911,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -950,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477326</v>
+        <v>477337</v>
       </c>
       <c r="R4" t="n">
-        <v>6593253</v>
+        <v>6593139</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -994,7 +995,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 57380-2020 artfynd.xlsx
+++ b/artfynd/A 57380-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121756651</v>
+        <v>121756618</v>
       </c>
       <c r="B2" t="n">
-        <v>56581</v>
+        <v>79232</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -731,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477348</v>
+        <v>477372</v>
       </c>
       <c r="R2" t="n">
-        <v>6592989</v>
+        <v>6593018</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -775,6 +762,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -793,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121756519</v>
+        <v>121756513</v>
       </c>
       <c r="B3" t="n">
-        <v>90719</v>
+        <v>74737</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -836,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477326</v>
+        <v>477390</v>
       </c>
       <c r="R3" t="n">
-        <v>6593253</v>
+        <v>6593251</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -899,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121756609</v>
+        <v>121756555</v>
       </c>
       <c r="B4" t="n">
-        <v>57369</v>
+        <v>78643</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,35 +903,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -951,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477337</v>
+        <v>477398</v>
       </c>
       <c r="R4" t="n">
-        <v>6593139</v>
+        <v>6593192</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -995,6 +974,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1013,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121756513</v>
+        <v>121756609</v>
       </c>
       <c r="B5" t="n">
-        <v>74733</v>
+        <v>57372</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,26 +1009,35 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1056,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477390</v>
+        <v>477337</v>
       </c>
       <c r="R5" t="n">
-        <v>6593251</v>
+        <v>6593139</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1100,7 +1089,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1119,10 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121756618</v>
+        <v>121756651</v>
       </c>
       <c r="B6" t="n">
-        <v>79228</v>
+        <v>56582</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,30 +1119,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1162,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477372</v>
+        <v>477348</v>
       </c>
       <c r="R6" t="n">
-        <v>6593018</v>
+        <v>6592989</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1206,7 +1207,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1228,7 +1228,7 @@
         <v>121756601</v>
       </c>
       <c r="B7" t="n">
-        <v>95687</v>
+        <v>95695</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1332,10 +1332,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121756555</v>
+        <v>121756519</v>
       </c>
       <c r="B8" t="n">
-        <v>78639</v>
+        <v>90726</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1344,25 +1344,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477398</v>
+        <v>477326</v>
       </c>
       <c r="R8" t="n">
-        <v>6593192</v>
+        <v>6593253</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>

--- a/artfynd/A 57380-2020 artfynd.xlsx
+++ b/artfynd/A 57380-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121756618</v>
+        <v>121756555</v>
       </c>
       <c r="B2" t="n">
-        <v>79232</v>
+        <v>78645</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477372</v>
+        <v>477398</v>
       </c>
       <c r="R2" t="n">
-        <v>6593018</v>
+        <v>6593192</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121756513</v>
+        <v>121756651</v>
       </c>
       <c r="B3" t="n">
-        <v>74737</v>
+        <v>56584</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,30 +793,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>308</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -824,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477390</v>
+        <v>477348</v>
       </c>
       <c r="R3" t="n">
-        <v>6593251</v>
+        <v>6592989</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -868,7 +881,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -887,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121756555</v>
+        <v>121756513</v>
       </c>
       <c r="B4" t="n">
-        <v>78643</v>
+        <v>74739</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -930,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477398</v>
+        <v>477390</v>
       </c>
       <c r="R4" t="n">
-        <v>6593192</v>
+        <v>6593251</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -993,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121756609</v>
+        <v>121756519</v>
       </c>
       <c r="B5" t="n">
-        <v>57372</v>
+        <v>90728</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,39 +1017,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1045,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477337</v>
+        <v>477326</v>
       </c>
       <c r="R5" t="n">
-        <v>6593139</v>
+        <v>6593253</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1089,6 +1092,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1107,10 +1111,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121756651</v>
+        <v>121756609</v>
       </c>
       <c r="B6" t="n">
-        <v>56582</v>
+        <v>57374</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,25 +1123,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1146,14 +1150,10 @@
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477348</v>
+        <v>477337</v>
       </c>
       <c r="R6" t="n">
-        <v>6592989</v>
+        <v>6593139</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1225,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121756601</v>
+        <v>121756618</v>
       </c>
       <c r="B7" t="n">
-        <v>95695</v>
+        <v>79234</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1241,27 +1241,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>54</v>
+        <v>229821</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogstrappmossa</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Anastrophyllum michauxii</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(F.Weber.) H.Buch</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1269,10 +1268,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477377</v>
+        <v>477372</v>
       </c>
       <c r="R7" t="n">
-        <v>6593144</v>
+        <v>6593018</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1332,10 +1331,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121756519</v>
+        <v>121756601</v>
       </c>
       <c r="B8" t="n">
-        <v>90726</v>
+        <v>95697</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1344,30 +1343,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>54</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skogstrappmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Anastrophyllum michauxii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(F.Weber.) H.Buch</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477326</v>
+        <v>477377</v>
       </c>
       <c r="R8" t="n">
-        <v>6593253</v>
+        <v>6593144</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>

--- a/artfynd/A 57380-2020 artfynd.xlsx
+++ b/artfynd/A 57380-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1436,6 +1436,124 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>122777316</v>
+      </c>
+      <c r="B9" t="n">
+        <v>56688</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Båshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>477356</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6593195</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 57380-2020 artfynd.xlsx
+++ b/artfynd/A 57380-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1554,6 +1554,118 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>123079041</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79384</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Märrsprängardrågen, Märrsprängardrågen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>477217</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6592835</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 57380-2020 artfynd.xlsx
+++ b/artfynd/A 57380-2020 artfynd.xlsx
@@ -1441,7 +1441,7 @@
         <v>122777316</v>
       </c>
       <c r="B9" t="n">
-        <v>56688</v>
+        <v>56691</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>123079041</v>
       </c>
       <c r="B10" t="n">
-        <v>79384</v>
+        <v>79387</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 57380-2020 artfynd.xlsx
+++ b/artfynd/A 57380-2020 artfynd.xlsx
@@ -1559,7 +1559,7 @@
         <v>123079041</v>
       </c>
       <c r="B10" t="n">
-        <v>79387</v>
+        <v>79389</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 57380-2020 artfynd.xlsx
+++ b/artfynd/A 57380-2020 artfynd.xlsx
@@ -1559,7 +1559,7 @@
         <v>123079041</v>
       </c>
       <c r="B10" t="n">
-        <v>79389</v>
+        <v>79390</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 57380-2020 artfynd.xlsx
+++ b/artfynd/A 57380-2020 artfynd.xlsx
@@ -1559,7 +1559,7 @@
         <v>123079041</v>
       </c>
       <c r="B10" t="n">
-        <v>79393</v>
+        <v>79399</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 57380-2020 artfynd.xlsx
+++ b/artfynd/A 57380-2020 artfynd.xlsx
@@ -1559,7 +1559,7 @@
         <v>123079041</v>
       </c>
       <c r="B10" t="n">
-        <v>79399</v>
+        <v>79404</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 57380-2020 artfynd.xlsx
+++ b/artfynd/A 57380-2020 artfynd.xlsx
@@ -1559,7 +1559,7 @@
         <v>123079041</v>
       </c>
       <c r="B10" t="n">
-        <v>79404</v>
+        <v>79406</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
